--- a/data/hotpatch-unsupported.xlsx
+++ b/data/hotpatch-unsupported.xlsx
@@ -789,7 +789,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -799,9 +799,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -813,9 +810,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1365,216 +1359,216 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" ht="10.2" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3" ht="10.2" spans="1:8">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>157</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>0.421</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="10"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" ht="20.4" spans="1:8">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>65</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>0.174</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="10"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" ht="30.6" spans="1:8">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>37</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>0.099</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="10"/>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" ht="20.4" spans="1:8">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>9</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>0.024</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="10"/>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" ht="10.2" spans="1:8">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>65</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>0.174</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" ht="10.2" spans="1:8">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>40</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>0.107</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="10"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" ht="10.2" spans="1:7">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="G10" s="11"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="7:7">
-      <c r="G11" s="11"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="7:7">
-      <c r="G12" s="11"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="7:7">
-      <c r="G13" s="11"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" spans="7:7">
-      <c r="G14" s="11"/>
+      <c r="G14" s="9"/>
     </row>
     <row r="15" spans="7:7">
-      <c r="G15" s="11"/>
+      <c r="G15" s="9"/>
     </row>
     <row r="16" spans="7:7">
-      <c r="G16" s="11"/>
+      <c r="G16" s="9"/>
     </row>
     <row r="17" spans="7:7">
-      <c r="G17" s="11"/>
+      <c r="G17" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
